--- a/data/correlation_analysis_timeout_zero.xlsx
+++ b/data/correlation_analysis_timeout_zero.xlsx
@@ -503,10 +503,10 @@
     <col min="6" max="6" width="21.7109375" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" customWidth="1"/>
     <col min="8" max="8" width="28.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
     <col min="10" max="10" width="21.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="20.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="12" max="12" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -696,7 +696,7 @@
         <v>-0.3178304128441319</v>
       </c>
       <c r="L5">
-        <v>0.3140610795011265</v>
+        <v>0.3140610795011266</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -833,22 +833,22 @@
         <v>92</v>
       </c>
       <c r="G9">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H9">
         <v>100</v>
       </c>
       <c r="I9">
-        <v>-0.2232481170885827</v>
+        <v>-0.2266499931585039</v>
       </c>
       <c r="J9">
-        <v>0.001636069376151588</v>
+        <v>0.001388944087542739</v>
       </c>
       <c r="K9">
-        <v>-0.3234519555354279</v>
+        <v>-0.3292121926341289</v>
       </c>
       <c r="L9">
-        <v>0.001028681640569814</v>
+        <v>0.0008243882531155807</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -871,22 +871,22 @@
         <v>46</v>
       </c>
       <c r="G10">
-        <v>794</v>
+        <v>768</v>
       </c>
       <c r="H10">
         <v>50</v>
       </c>
       <c r="I10">
-        <v>-0.05768310136706124</v>
+        <v>0.01866777293784236</v>
       </c>
       <c r="J10">
-        <v>0.5808166089173682</v>
+        <v>0.8583574614657677</v>
       </c>
       <c r="K10">
-        <v>-0.06873895440322977</v>
+        <v>0.02926774595311432</v>
       </c>
       <c r="L10">
-        <v>0.635267646345926</v>
+        <v>0.8401020874019567</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -909,22 +909,22 @@
         <v>46</v>
       </c>
       <c r="G11">
-        <v>794</v>
+        <v>768</v>
       </c>
       <c r="H11">
         <v>50</v>
       </c>
       <c r="I11">
-        <v>-0.03854494781179903</v>
+        <v>0.03525306566614442</v>
       </c>
       <c r="J11">
-        <v>0.6995394491817443</v>
+        <v>0.7244530391680126</v>
       </c>
       <c r="K11">
-        <v>-0.04832503745113209</v>
+        <v>0.03962642574794883</v>
       </c>
       <c r="L11">
-        <v>0.7389368221688255</v>
+        <v>0.7846830695577185</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -947,22 +947,22 @@
         <v>46</v>
       </c>
       <c r="G12">
-        <v>794</v>
+        <v>768</v>
       </c>
       <c r="H12">
         <v>50</v>
       </c>
       <c r="I12">
-        <v>0.1156617751198898</v>
+        <v>0.1975428742000058</v>
       </c>
       <c r="J12">
-        <v>0.2438312496350385</v>
+        <v>0.04682237144660668</v>
       </c>
       <c r="K12">
-        <v>0.1718948469712283</v>
+        <v>0.2832674538277786</v>
       </c>
       <c r="L12">
-        <v>0.2326162766495191</v>
+        <v>0.04622012001137949</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -985,22 +985,22 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H13">
         <v>10</v>
       </c>
       <c r="I13">
-        <v>-0.3373495424699933</v>
+        <v>-0.5284193913361779</v>
       </c>
       <c r="J13">
-        <v>0.2074202127647988</v>
+        <v>0.05682819683984795</v>
       </c>
       <c r="K13">
-        <v>-0.4296689244236597</v>
+        <v>-0.6292532049656926</v>
       </c>
       <c r="L13">
-        <v>0.215243543278886</v>
+        <v>0.05126402824042627</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1023,22 +1023,22 @@
         <v>10</v>
       </c>
       <c r="G14">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H14">
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-0.1816497536376887</v>
+        <v>-0.4662524041201569</v>
       </c>
       <c r="J14">
-        <v>0.4972433060612282</v>
+        <v>0.09284922807157968</v>
       </c>
       <c r="K14">
-        <v>-0.2669155439601523</v>
+        <v>-0.5618332187193684</v>
       </c>
       <c r="L14">
-        <v>0.4559719917038285</v>
+        <v>0.090982576216914</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1061,22 +1061,22 @@
         <v>10</v>
       </c>
       <c r="G15">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H15">
         <v>10</v>
       </c>
       <c r="I15">
-        <v>-0.0524863881081478</v>
+        <v>-0.3143473067309657</v>
       </c>
       <c r="J15">
-        <v>0.8456867367859529</v>
+        <v>0.2610207247026572</v>
       </c>
       <c r="K15">
-        <v>-0.06856450678985078</v>
+        <v>-0.3719387243003159</v>
       </c>
       <c r="L15">
-        <v>0.8507182473580949</v>
+        <v>0.2899037448075479</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1099,22 +1099,22 @@
         <v>10</v>
       </c>
       <c r="G16">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H16">
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-0.7525489793561388</v>
+        <v>-0.5905863785521988</v>
       </c>
       <c r="J16">
-        <v>0.004918698145511134</v>
+        <v>0.03327875704510121</v>
       </c>
       <c r="K16">
-        <v>-0.8788682545029405</v>
+        <v>-0.6741998624632421</v>
       </c>
       <c r="L16">
-        <v>0.000811787483996615</v>
+        <v>0.03251559932021606</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1137,22 +1137,22 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H17">
         <v>10</v>
       </c>
       <c r="I17">
-        <v>-0.1816497536376887</v>
+        <v>0.03108349360801046</v>
       </c>
       <c r="J17">
-        <v>0.4972433060612282</v>
+        <v>0.9107940274245708</v>
       </c>
       <c r="K17">
-        <v>-0.260405408741612</v>
+        <v>0.02247332874877474</v>
       </c>
       <c r="L17">
-        <v>0.4674445466605421</v>
+        <v>0.9508644143273767</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1175,22 +1175,22 @@
         <v>10</v>
       </c>
       <c r="G18">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H18">
         <v>10</v>
       </c>
       <c r="I18">
-        <v>0.4411494016915297</v>
+        <v>0.404085416904136</v>
       </c>
       <c r="J18">
-        <v>0.09923045565594253</v>
+        <v>0.1452595077432854</v>
       </c>
       <c r="K18">
-        <v>0.5143006822646836</v>
+        <v>0.4944132324730443</v>
       </c>
       <c r="L18">
-        <v>0.1282920587230653</v>
+        <v>0.1463267160789159</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1213,22 +1213,22 @@
         <v>10</v>
       </c>
       <c r="G19">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H19">
         <v>10</v>
       </c>
       <c r="I19">
-        <v>0.4198911048651824</v>
+        <v>0.4400862294233521</v>
       </c>
       <c r="J19">
-        <v>0.1194709867717007</v>
+        <v>0.1155858306979473</v>
       </c>
       <c r="K19">
-        <v>0.5060713596393749</v>
+        <v>0.5297309103671165</v>
       </c>
       <c r="L19">
-        <v>0.1355782583455031</v>
+        <v>0.1152952650343875</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1251,22 +1251,22 @@
         <v>10</v>
       </c>
       <c r="G20">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H20">
         <v>10</v>
       </c>
       <c r="I20">
-        <v>-0.3892494720807615</v>
+        <v>-0.404085416904136</v>
       </c>
       <c r="J20">
-        <v>0.1457680056362324</v>
+        <v>0.1452595077432854</v>
       </c>
       <c r="K20">
-        <v>-0.5077905470461433</v>
+        <v>-0.4494665749754947</v>
       </c>
       <c r="L20">
-        <v>0.1340355823255553</v>
+        <v>0.1925017251163437</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1289,22 +1289,22 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H21">
         <v>10</v>
       </c>
       <c r="I21">
-        <v>-0.3373495424699933</v>
+        <v>-0.2175844552560732</v>
       </c>
       <c r="J21">
-        <v>0.2074202127647988</v>
+        <v>0.4328879340133424</v>
       </c>
       <c r="K21">
-        <v>-0.4687297357349016</v>
+        <v>-0.3146266024828463</v>
       </c>
       <c r="L21">
-        <v>0.1717865787289185</v>
+        <v>0.3759325783116143</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1327,22 +1327,22 @@
         <v>10</v>
       </c>
       <c r="G22">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H22">
         <v>10</v>
       </c>
       <c r="I22">
-        <v>0.0778498944161523</v>
+        <v>-0.2175844552560732</v>
       </c>
       <c r="J22">
-        <v>0.7711058640185235</v>
+        <v>0.4328879340133424</v>
       </c>
       <c r="K22">
-        <v>0.09765202827810447</v>
+        <v>-0.2696799449852968</v>
       </c>
       <c r="L22">
-        <v>0.788411563708648</v>
+        <v>0.4511390079856625</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1365,22 +1365,22 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H23">
         <v>10</v>
       </c>
       <c r="I23">
-        <v>0.1297498240269205</v>
+        <v>-0.1554174680400523</v>
       </c>
       <c r="J23">
-        <v>0.6277606629910362</v>
+        <v>0.5753530764008791</v>
       </c>
       <c r="K23">
-        <v>0.2083243269932896</v>
+        <v>-0.1573133012414231</v>
       </c>
       <c r="L23">
-        <v>0.5635582121900502</v>
+        <v>0.6642676178335104</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1403,22 +1403,22 @@
         <v>10</v>
       </c>
       <c r="G24">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H24">
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-0.2335496832484569</v>
+        <v>-0.03108349360801046</v>
       </c>
       <c r="J24">
-        <v>0.3827797056047885</v>
+        <v>0.9107940274245708</v>
       </c>
       <c r="K24">
-        <v>-0.3320168961455552</v>
+        <v>-0.04494665749754947</v>
       </c>
       <c r="L24">
-        <v>0.3486190102393061</v>
+        <v>0.9018775739844269</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1438,25 +1438,25 @@
         <v>16</v>
       </c>
       <c r="F25">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G25">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="H25">
         <v>16</v>
       </c>
       <c r="I25">
-        <v>-0.1807753815155468</v>
+        <v>-0.3208833147655317</v>
       </c>
       <c r="J25">
-        <v>0.3541954904764164</v>
+        <v>0.1310095881916458</v>
       </c>
       <c r="K25">
-        <v>-0.2576049186596542</v>
+        <v>-0.3615507630310936</v>
       </c>
       <c r="L25">
-        <v>0.3354345184285685</v>
+        <v>0.1688293942897778</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -1476,25 +1476,25 @@
         <v>16</v>
       </c>
       <c r="F26">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G26">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="H26">
         <v>16</v>
       </c>
       <c r="I26">
-        <v>-0.1807753815155468</v>
+        <v>-0.1544993737759967</v>
       </c>
       <c r="J26">
-        <v>0.3541954904764164</v>
+        <v>0.4671641537476017</v>
       </c>
       <c r="K26">
-        <v>-0.2666436877354316</v>
+        <v>-0.1717366124397695</v>
       </c>
       <c r="L26">
-        <v>0.3181414648703181</v>
+        <v>0.5247923002825454</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1514,25 +1514,25 @@
         <v>16</v>
       </c>
       <c r="F27">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G27">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="H27">
         <v>16</v>
       </c>
       <c r="I27">
-        <v>0.3539900381483285</v>
+        <v>0.3341631412724104</v>
       </c>
       <c r="J27">
-        <v>0.07056136851892029</v>
+        <v>0.1170517823729769</v>
       </c>
       <c r="K27">
-        <v>0.4341802833034056</v>
+        <v>0.3934758817437114</v>
       </c>
       <c r="L27">
-        <v>0.09288178063084394</v>
+        <v>0.1315976135653158</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -1552,25 +1552,25 @@
         <v>16</v>
       </c>
       <c r="F28">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G28">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="H28">
         <v>16</v>
       </c>
       <c r="I28">
-        <v>-0.1647705109143269</v>
+        <v>-0.4694027940381773</v>
       </c>
       <c r="J28">
-        <v>0.4027546538976249</v>
+        <v>0.0286729854548637</v>
       </c>
       <c r="K28">
-        <v>-0.2493004677260264</v>
+        <v>-0.5439282932204211</v>
       </c>
       <c r="L28">
-        <v>0.3517858440384553</v>
+        <v>0.0294039628831014</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -1590,25 +1590,25 @@
         <v>16</v>
       </c>
       <c r="F29">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G29">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="H29">
         <v>16</v>
       </c>
       <c r="I29">
-        <v>-0.1265427670608828</v>
+        <v>0.05942283606769105</v>
       </c>
       <c r="J29">
-        <v>0.5166373798159882</v>
+        <v>0.77974282876954</v>
       </c>
       <c r="K29">
-        <v>-0.1491396897503261</v>
+        <v>0.05423261445466403</v>
       </c>
       <c r="L29">
-        <v>0.5814513259975999</v>
+        <v>0.841887936826351</v>
       </c>
     </row>
   </sheetData>
@@ -1946,25 +1946,25 @@
         <v>50</v>
       </c>
       <c r="F10">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G10">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="H10">
         <v>50</v>
       </c>
       <c r="I10">
-        <v>-0.2741939043543897</v>
+        <v>-0.1513701890060563</v>
       </c>
       <c r="J10">
-        <v>0.01523742906785629</v>
+        <v>0.1849849928400071</v>
       </c>
       <c r="K10">
-        <v>-0.3438060590640694</v>
+        <v>-0.1909099024833014</v>
       </c>
       <c r="L10">
-        <v>0.0145005762354219</v>
+        <v>0.1841630933746127</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1984,25 +1984,25 @@
         <v>50</v>
       </c>
       <c r="F11">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G11">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="H11">
         <v>50</v>
       </c>
       <c r="I11">
-        <v>-0.2885159533670518</v>
+        <v>-0.1912266713473635</v>
       </c>
       <c r="J11">
-        <v>0.007534224862278689</v>
+        <v>0.07966527054092901</v>
       </c>
       <c r="K11">
-        <v>-0.3916527812158478</v>
+        <v>-0.2629384536176831</v>
       </c>
       <c r="L11">
-        <v>0.00491305256761129</v>
+        <v>0.06506084897945322</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2022,25 +2022,25 @@
         <v>50</v>
       </c>
       <c r="F12">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G12">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="H12">
         <v>50</v>
       </c>
       <c r="I12">
-        <v>0.1527404930393114</v>
+        <v>0.2310064793132821</v>
       </c>
       <c r="J12">
-        <v>0.1545006958890939</v>
+        <v>0.03309841101323721</v>
       </c>
       <c r="K12">
-        <v>0.1874148805812322</v>
+        <v>0.2844439628835274</v>
       </c>
       <c r="L12">
-        <v>0.192476549579598</v>
+        <v>0.04528302631069108</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2060,25 +2060,25 @@
         <v>10</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H13">
         <v>10</v>
       </c>
       <c r="I13">
-        <v>0.3651483716701108</v>
+        <v>0.07453559924999299</v>
       </c>
       <c r="J13">
-        <v>0.2008251226951454</v>
+        <v>0.794002680192762</v>
       </c>
       <c r="K13">
-        <v>0.4264014327112208</v>
+        <v>0.08703882797784893</v>
       </c>
       <c r="L13">
-        <v>0.2191383605228726</v>
+        <v>0.8110384240587123</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -2098,25 +2098,25 @@
         <v>10</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H14">
         <v>10</v>
       </c>
       <c r="I14">
-        <v>0.7302967433402215</v>
+        <v>0.3726779962499649</v>
       </c>
       <c r="J14">
-        <v>0.01051524593585891</v>
+        <v>0.191694602051888</v>
       </c>
       <c r="K14">
-        <v>0.8528028654224417</v>
+        <v>0.4351941398892446</v>
       </c>
       <c r="L14">
-        <v>0.001712874149321468</v>
+        <v>0.2087486300875882</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2136,25 +2136,25 @@
         <v>10</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15">
         <v>10</v>
       </c>
       <c r="I15">
-        <v>0.7385489458759965</v>
+        <v>0.3768891807222045</v>
       </c>
       <c r="J15">
-        <v>0.01028204822194895</v>
+        <v>0.1903458092612167</v>
       </c>
       <c r="K15">
-        <v>0.8553989227683017</v>
+        <v>0.4365189348559864</v>
       </c>
       <c r="L15">
-        <v>0.001600453316805279</v>
+        <v>0.2072083540976897</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2174,25 +2174,25 @@
         <v>10</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H16">
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-0.1217161238900369</v>
+        <v>0.149071198499986</v>
       </c>
       <c r="J16">
-        <v>0.6698153575994166</v>
+        <v>0.6015081344405899</v>
       </c>
       <c r="K16">
-        <v>-0.1421338109037403</v>
+        <v>0.1740776559556979</v>
       </c>
       <c r="L16">
-        <v>0.6952876854012655</v>
+        <v>0.6305360755569764</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -2212,25 +2212,25 @@
         <v>10</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H17">
         <v>10</v>
       </c>
       <c r="I17">
-        <v>-0.5477225575051662</v>
+        <v>-0.223606797749979</v>
       </c>
       <c r="J17">
-        <v>0.05500883362926572</v>
+        <v>0.4334219309560737</v>
       </c>
       <c r="K17">
-        <v>-0.6396021490668313</v>
+        <v>-0.2611164839335468</v>
       </c>
       <c r="L17">
-        <v>0.04643461767158175</v>
+        <v>0.4661852835040308</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -2250,25 +2250,25 @@
         <v>10</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H18">
         <v>10</v>
       </c>
       <c r="I18">
-        <v>-0.3651483716701108</v>
+        <v>-0.4472135954999579</v>
       </c>
       <c r="J18">
-        <v>0.2008251226951454</v>
+        <v>0.117185087198138</v>
       </c>
       <c r="K18">
-        <v>-0.4264014327112208</v>
+        <v>-0.5222329678670935</v>
       </c>
       <c r="L18">
-        <v>0.2191383605228726</v>
+        <v>0.1215029188171132</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -2288,25 +2288,25 @@
         <v>10</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H19">
         <v>10</v>
       </c>
       <c r="I19">
-        <v>-0.3077287274483319</v>
+        <v>-0.3015113445777636</v>
       </c>
       <c r="J19">
-        <v>0.2849576406684299</v>
+        <v>0.2948019919337048</v>
       </c>
       <c r="K19">
-        <v>-0.3564162178201257</v>
+        <v>-0.3492151478847891</v>
       </c>
       <c r="L19">
-        <v>0.312061132326838</v>
+        <v>0.3226327672991101</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -2326,25 +2326,25 @@
         <v>10</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H20">
         <v>10</v>
       </c>
       <c r="I20">
-        <v>0.3042903097250923</v>
+        <v>0.4472135954999579</v>
       </c>
       <c r="J20">
-        <v>0.2864220227778588</v>
+        <v>0.117185087198138</v>
       </c>
       <c r="K20">
-        <v>0.3553345272593507</v>
+        <v>0.5222329678670935</v>
       </c>
       <c r="L20">
-        <v>0.3136373640754537</v>
+        <v>0.1215029188171132</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -2364,25 +2364,25 @@
         <v>10</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H21">
         <v>10</v>
       </c>
       <c r="I21">
-        <v>-0.3651483716701108</v>
+        <v>-0.223606797749979</v>
       </c>
       <c r="J21">
-        <v>0.2008251226951454</v>
+        <v>0.4334219309560737</v>
       </c>
       <c r="K21">
-        <v>-0.4264014327112208</v>
+        <v>-0.2611164839335468</v>
       </c>
       <c r="L21">
-        <v>0.2191383605228726</v>
+        <v>0.4661852835040308</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -2402,25 +2402,25 @@
         <v>10</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H22">
         <v>10</v>
       </c>
       <c r="I22">
-        <v>0.3042903097250923</v>
+        <v>-0.223606797749979</v>
       </c>
       <c r="J22">
-        <v>0.2864220227778588</v>
+        <v>0.4334219309560737</v>
       </c>
       <c r="K22">
-        <v>0.3553345272593507</v>
+        <v>-0.2611164839335468</v>
       </c>
       <c r="L22">
-        <v>0.3136373640754537</v>
+        <v>0.4661852835040308</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -2440,25 +2440,25 @@
         <v>10</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H23">
         <v>10</v>
       </c>
       <c r="I23">
-        <v>0.3651483716701108</v>
+        <v>-0.149071198499986</v>
       </c>
       <c r="J23">
-        <v>0.2008251226951454</v>
+        <v>0.6015081344405899</v>
       </c>
       <c r="K23">
-        <v>0.4264014327112208</v>
+        <v>-0.1740776559556979</v>
       </c>
       <c r="L23">
-        <v>0.2191383605228726</v>
+        <v>0.6305360755569764</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -2478,25 +2478,25 @@
         <v>10</v>
       </c>
       <c r="F24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H24">
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-0.4260064336151292</v>
+        <v>-0.07453559924999299</v>
       </c>
       <c r="J24">
-        <v>0.1355930012663022</v>
+        <v>0.794002680192762</v>
       </c>
       <c r="K24">
-        <v>-0.497468338163091</v>
+        <v>-0.08703882797784893</v>
       </c>
       <c r="L24">
-        <v>0.1434614655950857</v>
+        <v>0.8110384240587123</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -2707,9 +2707,9 @@
     <col min="6" max="6" width="21.7109375" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" customWidth="1"/>
     <col min="8" max="8" width="28.7109375" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="10" width="20.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
     <col min="12" max="12" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3075,22 +3075,22 @@
         <v>40</v>
       </c>
       <c r="G10">
-        <v>537</v>
+        <v>522</v>
       </c>
       <c r="H10">
         <v>50</v>
       </c>
       <c r="I10">
-        <v>0.03324642499485375</v>
+        <v>0.08712167584961492</v>
       </c>
       <c r="J10">
-        <v>0.7524695495544889</v>
+        <v>0.4083766752312095</v>
       </c>
       <c r="K10">
-        <v>0.05369692827151148</v>
+        <v>0.1227687641955272</v>
       </c>
       <c r="L10">
-        <v>0.7111154281850389</v>
+        <v>0.3956759834281137</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -3113,22 +3113,22 @@
         <v>40</v>
       </c>
       <c r="G11">
-        <v>537</v>
+        <v>522</v>
       </c>
       <c r="H11">
         <v>50</v>
       </c>
       <c r="I11">
-        <v>0.02630142666529713</v>
+        <v>0.07462967377124524</v>
       </c>
       <c r="J11">
-        <v>0.7941029996140164</v>
+        <v>0.4588124610579571</v>
       </c>
       <c r="K11">
-        <v>0.0345247475921612</v>
+        <v>0.09255821810809323</v>
       </c>
       <c r="L11">
-        <v>0.8118632018166435</v>
+        <v>0.5226237277667096</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -3151,22 +3151,22 @@
         <v>40</v>
       </c>
       <c r="G12">
-        <v>537</v>
+        <v>522</v>
       </c>
       <c r="H12">
         <v>50</v>
       </c>
       <c r="I12">
-        <v>0.02696081483975262</v>
+        <v>0.0648462728029752</v>
       </c>
       <c r="J12">
-        <v>0.7877495099042957</v>
+        <v>0.5171200381290717</v>
       </c>
       <c r="K12">
-        <v>0.03904490288887924</v>
+        <v>0.08638478532010939</v>
       </c>
       <c r="L12">
-        <v>0.7877690834629696</v>
+        <v>0.5508414269428876</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -3189,22 +3189,22 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H13">
         <v>10</v>
       </c>
       <c r="I13">
-        <v>-0.4787549991450212</v>
+        <v>-0.6366820122120065</v>
       </c>
       <c r="J13">
-        <v>0.07217560549492458</v>
+        <v>0.01869720062275651</v>
       </c>
       <c r="K13">
-        <v>-0.6292853089020909</v>
+        <v>-0.8019532181238483</v>
       </c>
       <c r="L13">
-        <v>0.05124855216842294</v>
+        <v>0.005259237421010194</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -3227,22 +3227,22 @@
         <v>10</v>
       </c>
       <c r="G14">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H14">
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-0.2267786838055363</v>
+        <v>-0.4705910525045265</v>
       </c>
       <c r="J14">
-        <v>0.3943870594034554</v>
+        <v>0.08219753762575091</v>
       </c>
       <c r="K14">
-        <v>-0.2860387767736777</v>
+        <v>-0.5414897797588377</v>
       </c>
       <c r="L14">
-        <v>0.4230203924441357</v>
+        <v>0.1059666504898876</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -3265,22 +3265,22 @@
         <v>10</v>
       </c>
       <c r="G15">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H15">
         <v>10</v>
       </c>
       <c r="I15">
-        <v>-0.1019294382875251</v>
+        <v>-0.3359355065735126</v>
       </c>
       <c r="J15">
-        <v>0.7040542681897126</v>
+        <v>0.218311625181403</v>
       </c>
       <c r="K15">
-        <v>-0.0765092055676006</v>
+        <v>-0.3506334920077187</v>
       </c>
       <c r="L15">
-        <v>0.8336123677972922</v>
+        <v>0.3205360031284263</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -3303,22 +3303,22 @@
         <v>10</v>
       </c>
       <c r="G16">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H16">
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-0.579545525280815</v>
+        <v>-0.3598637460328732</v>
       </c>
       <c r="J16">
-        <v>0.02951512807757192</v>
+        <v>0.1838095557893692</v>
       </c>
       <c r="K16">
-        <v>-0.7119187333033755</v>
+        <v>-0.4592381676435712</v>
       </c>
       <c r="L16">
-        <v>0.02091481468718881</v>
+        <v>0.1818195500051732</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -3341,22 +3341,22 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H17">
         <v>10</v>
       </c>
       <c r="I17">
-        <v>-0.1259881576697424</v>
+        <v>0.08304547985373997</v>
       </c>
       <c r="J17">
-        <v>0.6360988735986226</v>
+        <v>0.7590571299004958</v>
       </c>
       <c r="K17">
-        <v>-0.1906925178491184</v>
+        <v>0.08910591312487204</v>
       </c>
       <c r="L17">
-        <v>0.5977007516614028</v>
+        <v>0.8066210879575378</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -3379,22 +3379,22 @@
         <v>10</v>
       </c>
       <c r="G18">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H18">
         <v>10</v>
       </c>
       <c r="I18">
-        <v>0.579545525280815</v>
+        <v>0.5259547057403532</v>
       </c>
       <c r="J18">
-        <v>0.02951512807757192</v>
+        <v>0.05206997227535645</v>
       </c>
       <c r="K18">
-        <v>0.7437008196115621</v>
+        <v>0.7128473049989763</v>
       </c>
       <c r="L18">
-        <v>0.01366958411527145</v>
+        <v>0.02067214786469852</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -3417,22 +3417,22 @@
         <v>10</v>
       </c>
       <c r="G19">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H19">
         <v>10</v>
       </c>
       <c r="I19">
-        <v>0.560611910581388</v>
+        <v>0.5598925109558542</v>
       </c>
       <c r="J19">
-        <v>0.0366903087793031</v>
+        <v>0.04019719781553128</v>
       </c>
       <c r="K19">
-        <v>0.7172738021962557</v>
+        <v>0.7253300668002809</v>
       </c>
       <c r="L19">
-        <v>0.01954204435368506</v>
+        <v>0.01759621904480188</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -3455,22 +3455,22 @@
         <v>10</v>
       </c>
       <c r="G20">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H20">
         <v>10</v>
       </c>
       <c r="I20">
-        <v>-0.4787549991450212</v>
+        <v>-0.4705910525045265</v>
       </c>
       <c r="J20">
-        <v>0.07217560549492458</v>
+        <v>0.08219753762575091</v>
       </c>
       <c r="K20">
-        <v>-0.6419981434253655</v>
+        <v>-0.5689069837972599</v>
       </c>
       <c r="L20">
-        <v>0.04536158917864154</v>
+        <v>0.08610936073892451</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -3493,22 +3493,22 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H21">
         <v>10</v>
       </c>
       <c r="I21">
-        <v>-0.2771739468734333</v>
+        <v>-0.1384091330895666</v>
       </c>
       <c r="J21">
-        <v>0.2978975979923409</v>
+        <v>0.6092119761915052</v>
       </c>
       <c r="K21">
-        <v>-0.3750286184365996</v>
+        <v>-0.1987747292785607</v>
       </c>
       <c r="L21">
-        <v>0.2855969029688312</v>
+        <v>0.5819571528087297</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -3531,22 +3531,22 @@
         <v>10</v>
       </c>
       <c r="G22">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H22">
         <v>10</v>
       </c>
       <c r="I22">
-        <v>0.1259881576697424</v>
+        <v>-0.1384091330895666</v>
       </c>
       <c r="J22">
-        <v>0.6360988735986226</v>
+        <v>0.6092119761915052</v>
       </c>
       <c r="K22">
-        <v>0.1461975970176575</v>
+        <v>-0.1919204282689551</v>
       </c>
       <c r="L22">
-        <v>0.6869410188538527</v>
+        <v>0.595298950736874</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -3569,22 +3569,22 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H23">
         <v>10</v>
       </c>
       <c r="I23">
-        <v>0.1259881576697424</v>
+        <v>-0.1384091330895666</v>
       </c>
       <c r="J23">
-        <v>0.6360988735986226</v>
+        <v>0.6092119761915052</v>
       </c>
       <c r="K23">
-        <v>0.2161181868956676</v>
+        <v>-0.1302317191825053</v>
       </c>
       <c r="L23">
-        <v>0.5487107060733141</v>
+        <v>0.7199008272052645</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -3607,22 +3607,22 @@
         <v>10</v>
       </c>
       <c r="G24">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H24">
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-0.2267786838055363</v>
+        <v>-0.02768182661791332</v>
       </c>
       <c r="J24">
-        <v>0.3943870594034554</v>
+        <v>0.9185663957730847</v>
       </c>
       <c r="K24">
-        <v>-0.3114644458202268</v>
+        <v>-0.02741720403842217</v>
       </c>
       <c r="L24">
-        <v>0.3810089567050594</v>
+        <v>0.9400699293286143</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -4196,7 +4196,7 @@
         <v>0.2933526131391836</v>
       </c>
       <c r="L12">
-        <v>0.03867934687031337</v>
+        <v>0.03867934687031339</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -4988,7 +4988,7 @@
         <v>-0.5561107852980067</v>
       </c>
       <c r="L7">
-        <v>0.0604349562009266</v>
+        <v>0.06043495620092659</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -5046,25 +5046,25 @@
         <v>100</v>
       </c>
       <c r="F9">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G9">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H9">
         <v>100</v>
       </c>
       <c r="I9">
-        <v>-0.1777071888309779</v>
+        <v>-0.1869261787362204</v>
       </c>
       <c r="J9">
-        <v>0.02109743444634812</v>
+        <v>0.01502626043323942</v>
       </c>
       <c r="K9">
-        <v>-0.2338626244994551</v>
+        <v>-0.2423346744391451</v>
       </c>
       <c r="L9">
-        <v>0.01919115836424928</v>
+        <v>0.01513196719297787</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -5084,25 +5084,25 @@
         <v>50</v>
       </c>
       <c r="F10">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G10">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H10">
         <v>50</v>
       </c>
       <c r="I10">
-        <v>-0.2254320318923924</v>
+        <v>-0.1665388026682479</v>
       </c>
       <c r="J10">
-        <v>0.03750206210014283</v>
+        <v>0.1280616578297019</v>
       </c>
       <c r="K10">
-        <v>-0.2757884146130811</v>
+        <v>-0.2014155913676093</v>
       </c>
       <c r="L10">
-        <v>0.05255329742499692</v>
+        <v>0.1607294756220496</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -5122,25 +5122,25 @@
         <v>50</v>
       </c>
       <c r="F11">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G11">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H11">
         <v>50</v>
       </c>
       <c r="I11">
-        <v>-0.1794340300657417</v>
+        <v>-0.1072157037809592</v>
       </c>
       <c r="J11">
-        <v>0.08321105252268295</v>
+        <v>0.3053256696332304</v>
       </c>
       <c r="K11">
-        <v>-0.2382169979796553</v>
+        <v>-0.1443212092158959</v>
       </c>
       <c r="L11">
-        <v>0.095728836361827</v>
+        <v>0.3173391327305688</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -5160,25 +5160,25 @@
         <v>50</v>
       </c>
       <c r="F12">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G12">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H12">
         <v>50</v>
       </c>
       <c r="I12">
-        <v>0.1869191683862415</v>
+        <v>0.2226979908645411</v>
       </c>
       <c r="J12">
-        <v>0.06934431565042681</v>
+        <v>0.03212529602718809</v>
       </c>
       <c r="K12">
-        <v>0.2610882725528407</v>
+        <v>0.3048932618757045</v>
       </c>
       <c r="L12">
-        <v>0.06704286140152567</v>
+        <v>0.03132317581227168</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -5201,22 +5201,22 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H13">
         <v>10</v>
       </c>
       <c r="I13">
-        <v>0.04969039949999533</v>
+        <v>0.05270462766947299</v>
       </c>
       <c r="J13">
-        <v>0.8509806870320558</v>
+        <v>0.8464505968765906</v>
       </c>
       <c r="K13">
-        <v>0.01262892050706804</v>
+        <v>0.0259499648053841</v>
       </c>
       <c r="L13">
-        <v>0.9723786419920799</v>
+        <v>0.9432726625041241</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -5239,22 +5239,22 @@
         <v>10</v>
       </c>
       <c r="G14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H14">
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-0.149071198499986</v>
+        <v>-0.2635231383473649</v>
       </c>
       <c r="J14">
-        <v>0.5730251193553904</v>
+        <v>0.3329216080655659</v>
       </c>
       <c r="K14">
-        <v>-0.1894338076060206</v>
+        <v>-0.3503245248726853</v>
       </c>
       <c r="L14">
-        <v>0.6001664342511973</v>
+        <v>0.3209921486658833</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -5277,22 +5277,22 @@
         <v>10</v>
       </c>
       <c r="G15">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H15">
         <v>10</v>
       </c>
       <c r="I15">
-        <v>-0.1256297269074015</v>
+        <v>-0.2398508059000617</v>
       </c>
       <c r="J15">
-        <v>0.6374017405958849</v>
+        <v>0.3819327979196356</v>
       </c>
       <c r="K15">
-        <v>-0.152008377581442</v>
+        <v>-0.3448837241706717</v>
       </c>
       <c r="L15">
-        <v>0.6750590889374006</v>
+        <v>0.3290799383310438</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -5315,22 +5315,22 @@
         <v>10</v>
       </c>
       <c r="G16">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H16">
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-0.298142396999972</v>
+        <v>-0.210818510677892</v>
       </c>
       <c r="J16">
-        <v>0.2596563563704499</v>
+        <v>0.4385780260809998</v>
       </c>
       <c r="K16">
-        <v>-0.3788676152120412</v>
+        <v>-0.259499648053841</v>
       </c>
       <c r="L16">
-        <v>0.2802942824523375</v>
+        <v>0.4690507582155354</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -5353,22 +5353,22 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H17">
         <v>10</v>
       </c>
       <c r="I17">
-        <v>-0.1987615979999813</v>
+        <v>-0.105409255338946</v>
       </c>
       <c r="J17">
-        <v>0.4523703606773608</v>
+        <v>0.6985353583033387</v>
       </c>
       <c r="K17">
-        <v>-0.3409808536908371</v>
+        <v>-0.1686747712349966</v>
       </c>
       <c r="L17">
-        <v>0.3349456951179903</v>
+        <v>0.6413437507268416</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -5391,22 +5391,22 @@
         <v>10</v>
       </c>
       <c r="G18">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H18">
         <v>10</v>
       </c>
       <c r="I18">
-        <v>0.149071198499986</v>
+        <v>0.105409255338946</v>
       </c>
       <c r="J18">
-        <v>0.5730251193553904</v>
+        <v>0.6985353583033387</v>
       </c>
       <c r="K18">
-        <v>0.1641759665918845</v>
+        <v>0.1037998592215364</v>
       </c>
       <c r="L18">
-        <v>0.6503895621649565</v>
+        <v>0.7753684943458543</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -5429,22 +5429,22 @@
         <v>10</v>
       </c>
       <c r="G19">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H19">
         <v>10</v>
       </c>
       <c r="I19">
-        <v>0.07537783614444091</v>
+        <v>0.0266500895444513</v>
       </c>
       <c r="J19">
-        <v>0.7773295263554205</v>
+        <v>0.9226081041997291</v>
       </c>
       <c r="K19">
-        <v>0.1076726007868547</v>
+        <v>0.04555068055084343</v>
       </c>
       <c r="L19">
-        <v>0.7671778789420547</v>
+        <v>0.9005643729271482</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -5467,22 +5467,22 @@
         <v>10</v>
       </c>
       <c r="G20">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H20">
         <v>10</v>
       </c>
       <c r="I20">
-        <v>-0.09938079899999065</v>
+        <v>-0.105409255338946</v>
       </c>
       <c r="J20">
-        <v>0.7071142312899612</v>
+        <v>0.6985353583033387</v>
       </c>
       <c r="K20">
-        <v>-0.1262892050706804</v>
+        <v>-0.07784989441615228</v>
       </c>
       <c r="L20">
-        <v>0.7281063840216824</v>
+        <v>0.8307317091592451</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -5505,22 +5505,22 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H21">
         <v>10</v>
       </c>
       <c r="I21">
-        <v>-0.149071198499986</v>
+        <v>-0.05270462766947299</v>
       </c>
       <c r="J21">
-        <v>0.5730251193553904</v>
+        <v>0.8464505968765906</v>
       </c>
       <c r="K21">
-        <v>-0.2399494896342928</v>
+        <v>-0.1037998592215364</v>
       </c>
       <c r="L21">
-        <v>0.5043017190353258</v>
+        <v>0.7753684943458543</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -5543,22 +5543,22 @@
         <v>10</v>
       </c>
       <c r="G22">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H22">
         <v>10</v>
       </c>
       <c r="I22">
-        <v>0.3975231959999626</v>
+        <v>0.3162277660168379</v>
       </c>
       <c r="J22">
-        <v>0.1328549557310538</v>
+        <v>0.2452781168067728</v>
       </c>
       <c r="K22">
-        <v>0.5304146612968577</v>
+        <v>0.3892494720807614</v>
       </c>
       <c r="L22">
-        <v>0.1147392659290222</v>
+        <v>0.2662240730692272</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -5581,22 +5581,22 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H23">
         <v>10</v>
       </c>
       <c r="I23">
-        <v>0.298142396999972</v>
+        <v>0.210818510677892</v>
       </c>
       <c r="J23">
-        <v>0.2596563563704499</v>
+        <v>0.4385780260809998</v>
       </c>
       <c r="K23">
-        <v>0.4041254562261773</v>
+        <v>0.2465246656511489</v>
       </c>
       <c r="L23">
-        <v>0.2467547295422347</v>
+        <v>0.492323476312569</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -5619,22 +5619,22 @@
         <v>10</v>
       </c>
       <c r="G24">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H24">
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-0.2484519974999766</v>
+        <v>-0.1581138830084189</v>
       </c>
       <c r="J24">
-        <v>0.347558036741169</v>
+        <v>0.5612758361345778</v>
       </c>
       <c r="K24">
-        <v>-0.4293832972403134</v>
+        <v>-0.259499648053841</v>
       </c>
       <c r="L24">
-        <v>0.2155824117700313</v>
+        <v>0.4690507582155354</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -5654,25 +5654,13 @@
         <v>16</v>
       </c>
       <c r="F25">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H25">
         <v>16</v>
-      </c>
-      <c r="I25">
-        <v>-0.31352722326441</v>
-      </c>
-      <c r="J25">
-        <v>0.1131685336545776</v>
-      </c>
-      <c r="K25">
-        <v>-0.4479914656638877</v>
-      </c>
-      <c r="L25">
-        <v>0.08182143505121871</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -5692,25 +5680,13 @@
         <v>16</v>
       </c>
       <c r="F26">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H26">
         <v>16</v>
-      </c>
-      <c r="I26">
-        <v>-0.3872983346207417</v>
-      </c>
-      <c r="J26">
-        <v>0.05036597579032801</v>
-      </c>
-      <c r="K26">
-        <v>-0.5070173682344674</v>
-      </c>
-      <c r="L26">
-        <v>0.04501930875693567</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -5730,25 +5706,13 @@
         <v>16</v>
       </c>
       <c r="F27">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H27">
         <v>16</v>
-      </c>
-      <c r="I27">
-        <v>0.08334047874242113</v>
-      </c>
-      <c r="J27">
-        <v>0.6747078413451294</v>
-      </c>
-      <c r="K27">
-        <v>0.08027373462987823</v>
-      </c>
-      <c r="L27">
-        <v>0.7675926515511813</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -5768,25 +5732,13 @@
         <v>16</v>
       </c>
       <c r="F28">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H28">
         <v>16</v>
-      </c>
-      <c r="I28">
-        <v>0.09338863578008762</v>
-      </c>
-      <c r="J28">
-        <v>0.6401498414586226</v>
-      </c>
-      <c r="K28">
-        <v>0.1305442024324843</v>
-      </c>
-      <c r="L28">
-        <v>0.6298840619248964</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -5806,25 +5758,13 @@
         <v>16</v>
       </c>
       <c r="F29">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G29">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H29">
         <v>16</v>
-      </c>
-      <c r="I29">
-        <v>0.1290994448735805</v>
-      </c>
-      <c r="J29">
-        <v>0.5142199988155506</v>
-      </c>
-      <c r="K29">
-        <v>0.1619428608987702</v>
-      </c>
-      <c r="L29">
-        <v>0.5490376092324329</v>
       </c>
     </row>
   </sheetData>
